--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20231.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20231.xlsx
@@ -567,10 +567,10 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -579,7 +579,7 @@
         <v>31</v>
       </c>
       <c r="G5">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>9.199999999999999</v>
@@ -698,10 +698,10 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E5">
         <v>31</v>
@@ -832,10 +832,10 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -844,7 +844,7 @@
         <v>31</v>
       </c>
       <c r="G5">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>9.199999999999999</v>

--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20231.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -85,19 +85,10 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>JORGE</t>
-  </si>
-  <si>
     <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
   </si>
 </sst>
 </file>
@@ -544,10 +535,10 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
         <v>23</v>
@@ -556,7 +547,7 @@
         <v>85.19</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -655,16 +646,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>97.73</v>
+      </c>
+      <c r="H3">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -678,16 +672,19 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>85.19</v>
+      </c>
+      <c r="H4">
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -701,16 +698,19 @@
         <v>31</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>31</v>
       </c>
-      <c r="E5">
-        <v>31</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -786,16 +786,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>97.73</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -809,10 +809,10 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
         <v>23</v>
@@ -821,7 +821,7 @@
         <v>85.19</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -847,7 +847,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>
@@ -857,7 +857,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -895,10 +895,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
         <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -907,29 +907,6 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920374</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20231.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -80,15 +80,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
   </si>
 </sst>
 </file>
@@ -795,7 +786,7 @@
         <v>97.73</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -812,16 +803,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>85.19</v>
+        <v>96.3</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -847,7 +838,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -857,7 +848,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -887,29 +878,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920126</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20231.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20231.xlsx
@@ -477,16 +477,22 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29</v>
+      </c>
+      <c r="G2">
+        <v>85.29000000000001</v>
+      </c>
+      <c r="H2">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -614,16 +620,22 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="G2">
+        <v>94.12</v>
+      </c>
+      <c r="H2">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -751,16 +763,22 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="G2">
+        <v>94.12</v>
+      </c>
+      <c r="H2">
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">

--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20231.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20231.xlsx
@@ -804,7 +804,7 @@
         <v>97.73</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -830,7 +830,7 @@
         <v>96.3</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -856,7 +856,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20231.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20231.xlsx
@@ -804,7 +804,7 @@
         <v>97.73</v>
       </c>
       <c r="H3">
-        <v>9.9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -830,7 +830,7 @@
         <v>96.3</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -856,7 +856,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
